--- a/output/graficos_dimensiones/comunal_d_env_a_2023_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2023_valparaiso.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:19</t>
+    <t xml:space="preserve">2026-09-10 01:33</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2023_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2023_valparaiso.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:33</t>
+    <t xml:space="preserve">2026-09-12 22:44</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2023_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2023_valparaiso.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 22:44</t>
+    <t xml:space="preserve">2026-09-24 00:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2023_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2023_valparaiso.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:12</t>
+    <t xml:space="preserve">2026-10-02 16:03</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2023_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2023_valparaiso.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 16:03</t>
+    <t xml:space="preserve">2026-10-04 10:45</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2023_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2023_valparaiso.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 10:45</t>
+    <t xml:space="preserve">2026-10-05 16:43</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
